--- a/Result/profitability/3293.xlsx
+++ b/Result/profitability/3293.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>2.76</v>
       </c>
       <c r="M2" t="n">
-        <v>8.661250000000001</v>
+        <v>9.146249999999998</v>
       </c>
       <c r="N2" t="n">
-        <v>95.57874999999999</v>
+        <v>95.74875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>3.17</v>
       </c>
       <c r="M3" t="n">
-        <v>8.09375</v>
+        <v>8.401249999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>93.29375</v>
+        <v>93.46124999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>3.36</v>
       </c>
       <c r="M4" t="n">
-        <v>7.3725</v>
+        <v>7.65625</v>
       </c>
       <c r="N4" t="n">
-        <v>91.16374999999999</v>
+        <v>91.18125000000001</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>4.19</v>
       </c>
       <c r="M5" t="n">
-        <v>6.73125</v>
+        <v>7.095</v>
       </c>
       <c r="N5" t="n">
-        <v>88.56374999999998</v>
+        <v>88.56375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>4.44</v>
       </c>
       <c r="M6" t="n">
-        <v>6.20125</v>
+        <v>6.412500000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>86.27500000000001</v>
+        <v>86.34375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>4.54</v>
       </c>
       <c r="M7" t="n">
-        <v>5.53125</v>
+        <v>5.65375</v>
       </c>
       <c r="N7" t="n">
-        <v>83.88124999999999</v>
+        <v>83.91125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,7 +1391,7 @@
         <v>4.78</v>
       </c>
       <c r="M8" t="n">
-        <v>4.8025</v>
+        <v>4.853750000000001</v>
       </c>
       <c r="N8" t="n">
         <v>81.62125</v>
@@ -1775,7 +1775,7 @@
         <v>4.28375</v>
       </c>
       <c r="N11" t="n">
-        <v>78.61624999999999</v>
+        <v>78.61625000000001</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1902,7 +1902,7 @@
         <v>4.19125</v>
       </c>
       <c r="N12" t="n">
-        <v>78.84875000000001</v>
+        <v>78.84875</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3293</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>6413</v>
+      </c>
+      <c r="D75" t="n">
+        <v>140</v>
+      </c>
+      <c r="E75" t="n">
+        <v>6274</v>
+      </c>
+      <c r="F75" t="n">
+        <v>97.81999999999999</v>
+      </c>
+      <c r="G75" t="n">
+        <v>3834</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>59.79%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>110</v>
+      </c>
+      <c r="J75" t="n">
+        <v>3945</v>
+      </c>
+      <c r="K75" t="n">
+        <v>3266</v>
+      </c>
+      <c r="L75" t="n">
+        <v>11.59</v>
+      </c>
+      <c r="M75" t="n">
+        <v>9.765000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>97.36624999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.4100000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.03667262969588547</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.3352534562211982</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
